--- a/tams-svreport-parent/tams-svreport-chb/src/main/resources/tpl/ChbInvestTrade001.xlsx
+++ b/tams-svreport-parent/tams-svreport-chb/src/main/resources/tpl/ChbInvestTrade001.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9300"/>
+    <workbookView windowWidth="23040" windowHeight="8700"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -90,6 +90,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">CNY </t>
     </r>
     <r>
@@ -104,6 +110,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">01 </t>
     </r>
     <r>
@@ -118,6 +130,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">HKD </t>
     </r>
     <r>
@@ -132,6 +150,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">02 </t>
     </r>
     <r>
@@ -146,6 +170,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">USD </t>
     </r>
     <r>
@@ -160,6 +190,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">03 </t>
     </r>
     <r>
@@ -174,6 +210,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">EUR </t>
     </r>
     <r>
@@ -188,6 +230,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">04 </t>
     </r>
     <r>
@@ -202,6 +250,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JPY </t>
     </r>
     <r>
@@ -216,6 +270,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">05 </t>
     </r>
     <r>
@@ -230,6 +290,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">MOP </t>
     </r>
     <r>
@@ -244,6 +310,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">06 </t>
     </r>
     <r>
@@ -258,6 +330,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">CHF </t>
     </r>
     <r>
@@ -272,6 +350,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">07 </t>
     </r>
     <r>
@@ -286,6 +370,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">GBP </t>
     </r>
     <r>
@@ -300,6 +390,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">08 </t>
     </r>
     <r>
@@ -314,6 +410,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">RUB </t>
     </r>
     <r>
@@ -328,6 +430,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">09 </t>
     </r>
     <r>
@@ -342,6 +450,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">CAD </t>
     </r>
     <r>
@@ -356,6 +470,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">10 </t>
     </r>
     <r>
@@ -370,6 +490,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">DKK </t>
     </r>
     <r>
@@ -384,6 +510,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">11 </t>
     </r>
     <r>
@@ -398,6 +530,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">AUD </t>
     </r>
     <r>
@@ -412,6 +550,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">12 </t>
     </r>
     <r>
@@ -426,6 +570,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">SEK </t>
     </r>
     <r>
@@ -440,6 +590,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">SGD </t>
     </r>
     <r>
@@ -454,6 +610,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">TWD </t>
     </r>
     <r>
@@ -468,6 +630,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">AED </t>
     </r>
     <r>
@@ -482,6 +650,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">AFN </t>
     </r>
     <r>
@@ -496,6 +670,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">ALL </t>
     </r>
     <r>
@@ -510,6 +690,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">AMD </t>
     </r>
     <r>
@@ -524,6 +710,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">ANG </t>
     </r>
     <r>
@@ -538,6 +730,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">AOA </t>
     </r>
     <r>
@@ -552,6 +750,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">ARS </t>
     </r>
     <r>
@@ -566,6 +770,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">AWG </t>
     </r>
     <r>
@@ -580,6 +790,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">AZN </t>
     </r>
     <r>
@@ -594,6 +810,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">BAM </t>
     </r>
     <r>
@@ -608,6 +830,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">BBD </t>
     </r>
     <r>
@@ -622,6 +850,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">BDT </t>
     </r>
     <r>
@@ -636,6 +870,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">BGN </t>
     </r>
     <r>
@@ -650,6 +890,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">BHD </t>
     </r>
     <r>
@@ -664,6 +910,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">BIF </t>
     </r>
     <r>
@@ -678,6 +930,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">BMD </t>
     </r>
     <r>
@@ -692,6 +950,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">BND </t>
     </r>
     <r>
@@ -706,6 +970,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">BOB </t>
     </r>
     <r>
@@ -720,6 +990,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">BOV </t>
     </r>
     <r>
@@ -752,6 +1028,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">BRL </t>
     </r>
     <r>
@@ -766,6 +1048,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">BSD </t>
     </r>
     <r>
@@ -780,6 +1068,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">BTN </t>
     </r>
     <r>
@@ -794,6 +1088,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">BWP </t>
     </r>
     <r>
@@ -808,6 +1108,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">BYR </t>
     </r>
     <r>
@@ -822,6 +1128,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">BZD </t>
     </r>
     <r>
@@ -836,6 +1148,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">CDF </t>
     </r>
     <r>
@@ -850,6 +1168,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>CHE WIR</t>
     </r>
     <r>
@@ -864,6 +1188,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>CHW WIR</t>
     </r>
     <r>
@@ -878,6 +1208,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">CLF </t>
     </r>
     <r>
@@ -910,6 +1246,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">CLP </t>
     </r>
     <r>
@@ -924,6 +1266,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">COP </t>
     </r>
     <r>
@@ -938,6 +1286,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">COU </t>
     </r>
     <r>
@@ -970,6 +1324,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">CRC </t>
     </r>
     <r>
@@ -984,6 +1344,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">CUC </t>
     </r>
     <r>
@@ -998,6 +1364,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">CUP </t>
     </r>
     <r>
@@ -1012,6 +1384,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">CVE </t>
     </r>
     <r>
@@ -1026,6 +1404,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">CZK </t>
     </r>
     <r>
@@ -1040,6 +1424,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">DJF </t>
     </r>
     <r>
@@ -1054,6 +1444,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">DOP </t>
     </r>
     <r>
@@ -1068,6 +1464,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">DZD </t>
     </r>
     <r>
@@ -1082,6 +1484,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">EGP </t>
     </r>
     <r>
@@ -1096,6 +1504,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">ERN </t>
     </r>
     <r>
@@ -1110,6 +1524,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">ETB </t>
     </r>
     <r>
@@ -1124,6 +1544,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">FJD </t>
     </r>
     <r>
@@ -1138,6 +1564,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">FKP </t>
     </r>
     <r>
@@ -1152,6 +1584,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">GEL </t>
     </r>
     <r>
@@ -1166,6 +1604,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">GHS </t>
     </r>
     <r>
@@ -1180,6 +1624,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">GIP </t>
     </r>
     <r>
@@ -1194,6 +1644,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">GMD </t>
     </r>
     <r>
@@ -1208,6 +1664,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">GNF </t>
     </r>
     <r>
@@ -1222,6 +1684,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">GTQ </t>
     </r>
     <r>
@@ -1236,6 +1704,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">GYD </t>
     </r>
     <r>
@@ -1250,6 +1724,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">HNL </t>
     </r>
     <r>
@@ -1264,6 +1744,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">HRK </t>
     </r>
     <r>
@@ -1278,6 +1764,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">HTG </t>
     </r>
     <r>
@@ -1292,6 +1784,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">HUF </t>
     </r>
     <r>
@@ -1306,6 +1804,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">IDR </t>
     </r>
     <r>
@@ -1320,6 +1824,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">ILS </t>
     </r>
     <r>
@@ -1334,6 +1844,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">INR </t>
     </r>
     <r>
@@ -1348,6 +1864,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">IQD </t>
     </r>
     <r>
@@ -1362,6 +1884,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">IRR </t>
     </r>
     <r>
@@ -1376,6 +1904,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">ISK </t>
     </r>
     <r>
@@ -1390,6 +1924,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JMD </t>
     </r>
     <r>
@@ -1404,6 +1944,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">JOD </t>
     </r>
     <r>
@@ -1418,6 +1964,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">KES </t>
     </r>
     <r>
@@ -1432,6 +1984,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">KGS </t>
     </r>
     <r>
@@ -1446,6 +2004,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">KHR </t>
     </r>
     <r>
@@ -1460,6 +2024,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">KMF </t>
     </r>
     <r>
@@ -1474,6 +2044,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">KPW </t>
     </r>
     <r>
@@ -1488,6 +2064,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">KRW </t>
     </r>
     <r>
@@ -1502,6 +2084,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">KWD </t>
     </r>
     <r>
@@ -1516,6 +2104,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">KYD </t>
     </r>
     <r>
@@ -1530,6 +2124,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">KZT </t>
     </r>
     <r>
@@ -1544,6 +2144,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">LAK </t>
     </r>
     <r>
@@ -1558,6 +2164,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">LBP </t>
     </r>
     <r>
@@ -1572,6 +2184,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">LKR </t>
     </r>
     <r>
@@ -1586,6 +2204,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">LRD </t>
     </r>
     <r>
@@ -1600,6 +2224,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">LSL </t>
     </r>
     <r>
@@ -1614,6 +2244,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">LYD </t>
     </r>
     <r>
@@ -1628,6 +2264,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">MAD </t>
     </r>
     <r>
@@ -1642,6 +2284,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">MDL </t>
     </r>
     <r>
@@ -1656,6 +2304,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">MGA </t>
     </r>
     <r>
@@ -1670,6 +2324,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">MKD </t>
     </r>
     <r>
@@ -1684,6 +2344,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">MMK </t>
     </r>
     <r>
@@ -1698,6 +2364,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">MNT </t>
     </r>
     <r>
@@ -1712,6 +2384,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">MRO </t>
     </r>
     <r>
@@ -1726,6 +2404,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">MUR </t>
     </r>
     <r>
@@ -1740,6 +2424,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">MVR </t>
     </r>
     <r>
@@ -1754,6 +2444,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">MWK </t>
     </r>
     <r>
@@ -1768,6 +2464,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">MXN </t>
     </r>
     <r>
@@ -1782,6 +2484,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">MXV </t>
     </r>
     <r>
@@ -1814,6 +2522,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">MYR </t>
     </r>
     <r>
@@ -1828,6 +2542,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">MZN </t>
     </r>
     <r>
@@ -1842,6 +2562,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">NAD </t>
     </r>
     <r>
@@ -1856,6 +2582,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">NGN </t>
     </r>
     <r>
@@ -1870,6 +2602,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">NIO </t>
     </r>
     <r>
@@ -1884,6 +2622,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">NOK </t>
     </r>
     <r>
@@ -1898,6 +2642,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">NPR </t>
     </r>
     <r>
@@ -1912,6 +2662,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">NZD </t>
     </r>
     <r>
@@ -1926,6 +2682,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">OMR </t>
     </r>
     <r>
@@ -1940,6 +2702,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">PAB </t>
     </r>
     <r>
@@ -1954,6 +2722,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">PEN </t>
     </r>
     <r>
@@ -1968,6 +2742,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">PGK </t>
     </r>
     <r>
@@ -1982,6 +2762,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">PHP </t>
     </r>
     <r>
@@ -1996,6 +2782,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">PKR </t>
     </r>
     <r>
@@ -2010,6 +2802,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">PLN </t>
     </r>
     <r>
@@ -2024,6 +2822,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">PYG </t>
     </r>
     <r>
@@ -2038,6 +2842,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">QAR </t>
     </r>
     <r>
@@ -2052,6 +2862,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">RON </t>
     </r>
     <r>
@@ -2066,6 +2882,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">RSD </t>
     </r>
     <r>
@@ -2080,6 +2902,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">RWF </t>
     </r>
     <r>
@@ -2094,6 +2922,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">SAR </t>
     </r>
     <r>
@@ -2108,6 +2942,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">SBD </t>
     </r>
     <r>
@@ -2122,6 +2962,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">SCR </t>
     </r>
     <r>
@@ -2136,6 +2982,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">SDG </t>
     </r>
     <r>
@@ -2150,6 +3002,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">SHP </t>
     </r>
     <r>
@@ -2164,6 +3022,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">SLL </t>
     </r>
     <r>
@@ -2178,6 +3042,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">SOS </t>
     </r>
     <r>
@@ -2192,6 +3062,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">SRD </t>
     </r>
     <r>
@@ -2206,6 +3082,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">SSP </t>
     </r>
     <r>
@@ -2220,6 +3102,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">STD </t>
     </r>
     <r>
@@ -2234,6 +3122,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">SVC </t>
     </r>
     <r>
@@ -2248,6 +3142,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">SYP </t>
     </r>
     <r>
@@ -2262,6 +3162,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">SZL </t>
     </r>
     <r>
@@ -2276,6 +3182,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">THB </t>
     </r>
     <r>
@@ -2290,6 +3202,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">TJS </t>
     </r>
     <r>
@@ -2304,6 +3222,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">TMT </t>
     </r>
     <r>
@@ -2318,6 +3242,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">TND </t>
     </r>
     <r>
@@ -2332,6 +3262,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">TOP </t>
     </r>
     <r>
@@ -2346,6 +3282,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">TRY </t>
     </r>
     <r>
@@ -2360,6 +3302,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">TTD </t>
     </r>
     <r>
@@ -2374,6 +3322,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">TZS </t>
     </r>
     <r>
@@ -2388,6 +3342,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">UAH </t>
     </r>
     <r>
@@ -2402,6 +3362,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">UGX </t>
     </r>
     <r>
@@ -2416,6 +3382,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">USN </t>
     </r>
     <r>
@@ -2430,6 +3402,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">UYI </t>
     </r>
     <r>
@@ -2462,6 +3440,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">UYU </t>
     </r>
     <r>
@@ -2476,6 +3460,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">UZS </t>
     </r>
     <r>
@@ -2490,6 +3480,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">VEF </t>
     </r>
     <r>
@@ -2504,6 +3500,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">VND </t>
     </r>
     <r>
@@ -2518,6 +3520,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">VUV </t>
     </r>
     <r>
@@ -2532,6 +3540,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">WST </t>
     </r>
     <r>
@@ -2546,6 +3560,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">XAF </t>
     </r>
     <r>
@@ -2560,6 +3580,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">XAG </t>
     </r>
     <r>
@@ -2574,6 +3600,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">XAU </t>
     </r>
     <r>
@@ -2588,6 +3620,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">XBA </t>
     </r>
     <r>
@@ -2602,6 +3640,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">XBB </t>
     </r>
     <r>
@@ -2616,6 +3660,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">XBC </t>
     </r>
     <r>
@@ -2648,6 +3698,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">XBD </t>
     </r>
     <r>
@@ -2680,6 +3736,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">XCD </t>
     </r>
     <r>
@@ -2694,6 +3756,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">XDR </t>
     </r>
     <r>
@@ -2708,6 +3776,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">XOF </t>
     </r>
     <r>
@@ -2722,6 +3796,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">XPD </t>
     </r>
     <r>
@@ -2736,6 +3816,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">XPF </t>
     </r>
     <r>
@@ -2768,6 +3854,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">XPT </t>
     </r>
     <r>
@@ -2782,6 +3874,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">XSU </t>
     </r>
     <r>
@@ -2796,6 +3894,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">XTS </t>
     </r>
     <r>
@@ -2810,6 +3914,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">XUA </t>
     </r>
     <r>
@@ -2824,6 +3934,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">XXX </t>
     </r>
     <r>
@@ -2838,6 +3954,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">YER </t>
     </r>
     <r>
@@ -2852,6 +3974,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">ZAR </t>
     </r>
     <r>
@@ -2866,6 +3994,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">ZMW </t>
     </r>
     <r>
@@ -2880,6 +4014,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF080808"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">ZWL </t>
     </r>
     <r>
@@ -2898,11 +4038,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -2927,30 +4067,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2963,9 +4094,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2980,31 +4141,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3016,8 +4156,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3025,7 +4182,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3033,31 +4190,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3091,7 +4231,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3103,13 +4297,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3121,55 +4321,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3181,49 +4333,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3241,13 +4351,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3259,13 +4399,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3285,22 +4425,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3335,6 +4470,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -3352,24 +4505,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3388,10 +4528,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3400,133 +4540,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3906,7 +5046,7 @@
     <col min="16" max="16" width="15.2685185185185" customWidth="1"/>
     <col min="17" max="17" width="9" style="3"/>
     <col min="19" max="19" width="9" style="3"/>
-    <col min="21" max="21" width="9" style="4"/>
+    <col min="21" max="21" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
